--- a/EXCEL/Data/Fravær_data/Fravær_overenskomst.xlsx
+++ b/EXCEL/Data/Fravær_data/Fravær_overenskomst.xlsx
@@ -52,7 +52,7 @@
     <t>Datasæt 00 2024</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.54.44</t>
+    <t>Kørsel 14.4.2026 12.27.30</t>
   </si>
   <si>
     <t/>
